--- a/data/KROON.xlsx
+++ b/data/KROON.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ea4a19649b5fa823/Documentos/TRABAJO/MEGALO/SELLOUT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="8_{17657911-FBDC-4890-8761-A30CF4D5D0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88714716-65AD-45A0-8EDE-FF468F2E0698}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{17657911-FBDC-4890-8761-A30CF4D5D0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F03217A-C86A-4FAF-848F-BC7DBEB14A9B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{15390907-E293-428A-912E-2571C4706E86}"/>
   </bookViews>
@@ -850,14 +850,16 @@
       <c r="J3" s="13">
         <v>2500</v>
       </c>
-      <c r="K3" s="13"/>
+      <c r="K3" s="13">
+        <v>2800</v>
+      </c>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
       <c r="O3" s="12"/>
       <c r="P3" s="26">
         <f t="shared" ref="P3:P11" si="0">SUM(D3:O3)</f>
-        <v>16000</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -891,13 +893,15 @@
       <c r="J4" s="23">
         <v>1500</v>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="23">
+        <v>1800</v>
+      </c>
       <c r="L4" s="23"/>
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
       <c r="P4" s="25">
         <f t="shared" si="0"/>
-        <v>11600</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -929,13 +933,15 @@
       <c r="J5" s="23">
         <v>600</v>
       </c>
-      <c r="K5" s="23"/>
+      <c r="K5" s="23">
+        <v>400</v>
+      </c>
       <c r="L5" s="23"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
       <c r="P5" s="25">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1131,7 +1137,7 @@
       </c>
       <c r="K12" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="L12" s="20">
         <f t="shared" si="1"/>
@@ -1150,8 +1156,8 @@
         <v>0</v>
       </c>
       <c r="P12" s="21">
-        <f t="shared" si="1"/>
-        <v>32300</v>
+        <f>SUM(P3:P11)</f>
+        <v>37300</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
